--- a/ksoft/docs/records/Finance_Modality_Enum.xlsx
+++ b/ksoft/docs/records/Finance_Modality_Enum.xlsx
@@ -1367,13 +1367,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8772EDEF-1F84-4E21-8554-7EF54259578E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B3B04E0-FD4C-46EC-8B1F-61081CE52C27}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A619D848-1A95-468F-A2D1-7BB2D213E8B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A44483F-8C67-44F5-A338-77BBD2AB8EA8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF414658-F041-41AE-9AE0-4D78685D30AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3400481A-BB0A-445A-A974-E8C31DBDDD97}"/>
 </file>
--- a/ksoft/docs/records/Finance_Modality_Enum.xlsx
+++ b/ksoft/docs/records/Finance_Modality_Enum.xlsx
@@ -1367,13 +1367,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B3B04E0-FD4C-46EC-8B1F-61081CE52C27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8772EDEF-1F84-4E21-8554-7EF54259578E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A44483F-8C67-44F5-A338-77BBD2AB8EA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A619D848-1A95-468F-A2D1-7BB2D213E8B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3400481A-BB0A-445A-A974-E8C31DBDDD97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF414658-F041-41AE-9AE0-4D78685D30AD}"/>
 </file>